--- a/excel/Best_Start_Academy_Result_System.xlsx
+++ b/excel/Best_Start_Academy_Result_System.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADDIS\Desktop\BEST START\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADDIS\Desktop\School-Result-Management-System\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1B9C85-1FEF-4A4C-B636-E79B91D4D255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5ABE14-76B1-40A2-AC2F-0B1F08EA7EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RESULT SHEET " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'RESULT SHEET '!$A$1:$M$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'RESULT SHEET '!$A$1:$Q$34</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -662,6 +662,47 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -669,95 +710,54 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1182,101 +1182,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="55"/>
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="55"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="32"/>
     </row>
     <row r="3" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="57" t="s">
+      <c r="A3" s="30"/>
+      <c r="B3" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="55"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="58" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="55"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="52" t="s">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="52"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
       <c r="L5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1296,48 +1296,48 @@
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45" t="s">
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45" t="s">
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="45" t="s">
+      <c r="K6" s="38"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="45"/>
+      <c r="O6" s="38"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="12"/>
       <c r="R6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
       <c r="Q7" s="13"/>
     </row>
     <row r="8" spans="1:18" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1985,154 +1985,154 @@
       <c r="Q22" s="21"/>
     </row>
     <row r="23" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="48" t="str">
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46" t="str">
         <f>IFERROR(ROUND(AVERAGE(G9:G21),2),"")</f>
         <v/>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="50"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="39"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="45"/>
       <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42">
         <f>IFERROR(SUM(L9:L21),"")</f>
         <v>0</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="23"/>
-      <c r="I24" s="30" t="s">
+      <c r="I24" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31" t="str">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42" t="str">
         <f>IFERROR(ROUND(AVERAGE(M9:M21),2),"")</f>
         <v/>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="23"/>
-      <c r="I25" s="30" t="s">
+      <c r="I25" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="42"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42">
         <f>COUNTIF(M9:M21,"&gt;=50")</f>
         <v>0</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="23"/>
-      <c r="I26" s="30" t="s">
+      <c r="I26" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="39"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45"/>
     </row>
     <row r="27" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42">
         <f>COUNTIFS(M9:M21,"&gt;="&amp;40,M9:M21,"&lt;"&amp;50)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="23"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
       <c r="M27" s="24"/>
-      <c r="P27" s="43" t="s">
+      <c r="P27" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="Q27" s="43"/>
+      <c r="Q27" s="55"/>
     </row>
     <row r="28" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42">
         <f>COUNTIF(M9:M21,"&lt;40")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="30" t="s">
+      <c r="I28" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="35"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="51"/>
       <c r="P28" s="28" t="s">
         <v>47</v>
       </c>
@@ -2143,20 +2143,20 @@
       <c r="U28" s="26"/>
     </row>
     <row r="29" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
       <c r="H29" s="27"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
       <c r="M29" s="27"/>
       <c r="P29" s="29" t="s">
         <v>50</v>
@@ -2168,23 +2168,23 @@
       <c r="U29" s="25"/>
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="39"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="45"/>
       <c r="P30" s="29" t="s">
         <v>53</v>
       </c>
@@ -2195,23 +2195,23 @@
       <c r="U30" s="25"/>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="35"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="51"/>
       <c r="P31" s="29" t="s">
         <v>56</v>
       </c>
@@ -2222,21 +2222,21 @@
       <c r="U31" s="25"/>
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="35"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="51"/>
       <c r="P32" s="29" t="s">
         <v>58</v>
       </c>
@@ -2260,31 +2260,18 @@
     <row r="38" spans="20:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="20:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e3HizsHstQPGd+2kHMOnqmepOQwM8FfAFbejGRVKBS1wPaNpBZQb4Qt+oP2131Kfng5W9RxdOTzqGGTEQ/G4lA==" saltValue="8w6NiBxX0nT8Zh+TO8PI/g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZSL9cJ5Tjy4t6r3tkbDZ6ezG/8wsBjkZ3CUGxf3AbnGy5of2MK5/MllrzPYyoBUVD6a0jI+052mlfLMqIZOQ2g==" saltValue="p7+SzL33ZE52J6df5yfVJA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="49">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="Q1:Q4"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B4:P4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B7:P7"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="I23:P23"/>
+    <mergeCell ref="D30:O30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="I29:L29"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="M25:O25"/>
     <mergeCell ref="P25:Q25"/>
@@ -2301,16 +2288,29 @@
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D30:O30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B7:P7"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="I23:P23"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="Q1:Q4"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Score Too High" error="1st CA must be 0 to 20." sqref="C9:C22" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2328,9 +2328,6 @@
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;LBEST START ACADEMY&amp;C&amp;A</oddFooter>
-  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>